--- a/survey_encoded.xlsx
+++ b/survey_encoded.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,88 +425,213 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P61"/>
+  <dimension ref="A1:AO61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>סוג הרשות</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>אשכול חברתי-כלכלי</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>דיוק מדידה</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>פער מול תקינה</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>משתני המשפחה משקפים מעמסה במוגבלויות</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>הכי משמעותי לעומס במוגבלויות</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>משתני המשפחה משקפים מעמסה באזרחים ותיקים</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>משתנה</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ערך משתנה</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>מאפייני אוכלוסייה_אוכלוסייה כללית</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>מאפייני אוכלוסייה_אוכלוסייה מעורבת</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>מאפייני אוכלוסייה_חברה חרדית</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>מאפייני אוכלוסייה_חברה ערבית</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>תחומי העומס_מוגבלויות</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>משתנים נוספים לעומס במוגבלויות_רמת תפקוד של האדם, מעורבות/תפקוד המשפחה, אינטנסיביות הליווי, תיאום בין־מערכתי</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>תחומי העומס_אזרחים ותיקים</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>תחומי העומס_חוק סדרי דין</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>תחומי העומס_חוק נוער</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>תחומי העומס_משפחה</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>תחומי העומס_תחום נוער וצעירים</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>משתנים נוספים לעומס במוגבלויות_טיפול לבני משפחה</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>משתנים נוספים לעומס במוגבלויות_זמינות שירותים</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>משתנים נוספים לעומס במוגבלויות_מורכבות המוגבלות</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>משתנים נוספים לעומס במוגבלויות_מעורבות/תפקוד המשפחה</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>משתנים נוספים לעומס במוגבלויות_רמת תפקוד</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>היבט נוסף במוגבלויות_מגוון השירותים שמקבל האדם</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>היבט נוסף במוגבלויות_הוצאה חוץ ביתית</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>היבט נוסף במוגבלויות_מעורבות עם בריאות הנפש</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>היבט נוסף במוגבלויות_מציאת מסגרת חינוכית</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>היבט נוסף במוגבלויות_בירוקרטיה</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>היבט נוסף במוגבלויות_הביקורים במסגרות</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>היבט נוסף במוגבלויות_הכשרה והתמקצעות</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>משתנים נוספים לעומס באזרחים ותיקים_עורף משפחתי</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>משתנים נוספים לעומס באזרחים ותיקים_קשר ופיקוח במסגרות</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>משתנים נוספים לעומס באזרחים ותיקים_טיפול לבני משפחה</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>משתנים נוספים לעומס באזרחים ותיקים_מענה בקהילה האזרחית</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>תחומים עם פער_חוק נוער</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>תחומים עם פער_חוק סדרי דין</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>תחומים עם פער_מוגבלויות</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>תחומים עם פער_אזרחים ותיקים</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>תחומים עם פער_משפחה</t>
         </is>
       </c>
     </row>
@@ -513,26 +650,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
+      <c r="I2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
@@ -541,12 +684,87 @@
         <v>0</v>
       </c>
       <c r="N2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
       </c>
       <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -565,40 +783,121 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>אותם הרכיבים כמו בתיק רגיל</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
       <c r="J3" t="b">
         <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
       </c>
       <c r="O3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -617,21 +916,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מורכבות של מוגבלות ונפש </t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
@@ -639,19 +944,94 @@
         <v>1</v>
       </c>
       <c r="L4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
       </c>
       <c r="O4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -669,41 +1049,122 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>זמינות שירותים הן ברמה מקומית והן אזורית. טיפול כולל בכל המשפחה ולא רק באדם עם מוגבלות</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
       </c>
       <c r="N5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="b">
         <v>0</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="b">
+        <v>1</v>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -721,32 +1182,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מחסור בכח אדם.ריבוי ועליה באבחונים אוטיזם.מחסור בעוס לחוק משה </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -755,12 +1222,87 @@
         <v>1</v>
       </c>
       <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
         <v>2</v>
@@ -773,29 +1315,35 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הליווי</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="b">
         <v>1</v>
@@ -804,15 +1352,90 @@
         <v>1</v>
       </c>
       <c r="O7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="b">
         <v>0</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>1</v>
+      </c>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="n">
         <v>5</v>
@@ -825,41 +1448,122 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הטיפול</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
       <c r="O8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -877,29 +1581,35 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">אנטנסיביות הטיפול שיכול לנבוע ולהיות מושפע מכל אחד מהמשתנים האחריםד מהמשתנים </t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>3</v>
       </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="b">
         <v>1</v>
@@ -908,15 +1618,90 @@
         <v>1</v>
       </c>
       <c r="O9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="n">
         <v>9</v>
@@ -929,26 +1714,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>מעורבות/ תפקוד המשפחה</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
       <c r="J10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -963,11 +1754,88 @@
         <v>0</v>
       </c>
       <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10" t="b">
+        <v>1</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
       <c r="B11" t="n">
         <v>9</v>
       </c>
@@ -979,23 +1847,29 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>בעיני - מציאת המענה למגבלה ( שירות , התאמת מסגרת)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
@@ -1004,15 +1878,90 @@
         <v>0</v>
       </c>
       <c r="M11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
       </c>
       <c r="P11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" t="b">
+        <v>1</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1031,26 +1980,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="I12" t="n">
         <v>5</v>
       </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
       <c r="J12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -1059,12 +2014,87 @@
         <v>0</v>
       </c>
       <c r="N12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
       </c>
       <c r="P12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1083,40 +2113,121 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>אותם הרכיבים כמו בתיק רגיל</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>4</v>
       </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
       </c>
       <c r="O13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1135,21 +2246,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מורכבות של מוגבלות ונפש </t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
         <v>4</v>
       </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
@@ -1157,19 +2274,94 @@
         <v>1</v>
       </c>
       <c r="L14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
       </c>
       <c r="O14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="b">
         <v>1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1187,41 +2379,122 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>זמינות שירותים הן ברמה מקומית והן אזורית. טיפול כולל בכל המשפחה ולא רק באדם עם מוגבלות</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
         <v>5</v>
       </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
       <c r="J15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="b">
         <v>0</v>
       </c>
       <c r="N15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
       </c>
       <c r="P15" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="W15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1239,32 +2512,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מחסור בכח אדם.ריבוי ועליה באבחונים אוטיזם.מחסור בעוס לחוק משה </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="I16" t="n">
         <v>5</v>
       </c>
-      <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
       <c r="J16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1273,12 +2552,87 @@
         <v>1</v>
       </c>
       <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" t="b">
+        <v>1</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17" t="n">
         <v>2</v>
@@ -1291,29 +2645,35 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הליווי</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="I17" t="n">
         <v>5</v>
       </c>
-      <c r="G17" t="b">
-        <v>1</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="b">
         <v>1</v>
@@ -1322,15 +2682,90 @@
         <v>1</v>
       </c>
       <c r="O17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="b">
         <v>0</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>1</v>
+      </c>
+      <c r="R17" t="b">
+        <v>1</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
+        <v>1</v>
+      </c>
+      <c r="V17" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B18" t="n">
         <v>5</v>
@@ -1343,41 +2778,122 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הטיפול</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="I18" t="n">
         <v>4</v>
       </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
       <c r="J18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
       </c>
       <c r="O18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>1</v>
+      </c>
+      <c r="R18" t="b">
+        <v>1</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1395,29 +2911,35 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">אנטנסיביות הטיפול שיכול לנבוע ולהיות מושפע מכל אחד מהמשתנים האחריםד מהמשתנים </t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="I19" t="n">
         <v>4</v>
       </c>
-      <c r="G19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="b">
         <v>1</v>
@@ -1426,15 +2948,90 @@
         <v>1</v>
       </c>
       <c r="O19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>1</v>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
@@ -1447,26 +3044,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>מעורבות/ תפקוד המשפחה</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="I20" t="n">
         <v>5</v>
       </c>
-      <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
       <c r="J20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1481,11 +3084,88 @@
         <v>0</v>
       </c>
       <c r="P20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
       <c r="B21" t="n">
         <v>9</v>
       </c>
@@ -1497,23 +3177,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>בעיני - מציאת המענה למגבלה ( שירות , התאמת מסגרת)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="I21" t="n">
         <v>5</v>
       </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
       <c r="J21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
@@ -1522,15 +3208,90 @@
         <v>0</v>
       </c>
       <c r="M21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
       </c>
       <c r="P21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>1</v>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1549,26 +3310,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="I22" t="n">
         <v>5</v>
       </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1577,12 +3344,87 @@
         <v>0</v>
       </c>
       <c r="N22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
       </c>
       <c r="P22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1601,40 +3443,121 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>אותם הרכיבים כמו בתיק רגיל</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="G23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
       </c>
       <c r="O23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1653,21 +3576,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מורכבות של מוגבלות ונפש </t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="I24" t="n">
         <v>4</v>
       </c>
-      <c r="G24" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" t="b">
-        <v>0</v>
-      </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
@@ -1675,19 +3604,94 @@
         <v>1</v>
       </c>
       <c r="L24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
       </c>
       <c r="O24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>1</v>
+      </c>
+      <c r="R24" t="b">
+        <v>1</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="b">
+        <v>1</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1705,41 +3709,122 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>זמינות שירותים הן ברמה מקומית והן אזורית. טיפול כולל בכל המשפחה ולא רק באדם עם מוגבלות</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
         </is>
       </c>
-      <c r="F25" t="n">
+      <c r="I25" t="n">
         <v>5</v>
       </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" t="b">
-        <v>0</v>
-      </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="b">
         <v>0</v>
       </c>
       <c r="N25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
       </c>
       <c r="P25" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1757,32 +3842,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מחסור בכח אדם.ריבוי ועליה באבחונים אוטיזם.מחסור בעוס לחוק משה </t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="I26" t="n">
         <v>4</v>
       </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
       <c r="J26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -1791,12 +3882,87 @@
         <v>1</v>
       </c>
       <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>1</v>
+      </c>
+      <c r="R26" t="b">
+        <v>1</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27" t="n">
         <v>2</v>
@@ -1809,29 +3975,35 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הליווי</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="I27" t="n">
         <v>4</v>
       </c>
-      <c r="G27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" t="b">
-        <v>1</v>
-      </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="b">
         <v>1</v>
@@ -1840,15 +4012,90 @@
         <v>1</v>
       </c>
       <c r="O27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" t="b">
         <v>0</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>1</v>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
+        <v>1</v>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" t="b">
+        <v>0</v>
+      </c>
+      <c r="X27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
@@ -1861,41 +4108,122 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הטיפול</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="I28" t="n">
         <v>4</v>
       </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
       <c r="J28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
       </c>
       <c r="O28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="W28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1913,29 +4241,35 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">אנטנסיביות הטיפול שיכול לנבוע ולהיות מושפע מכל אחד מהמשתנים האחריםד מהמשתנים </t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="I29" t="n">
         <v>4</v>
       </c>
-      <c r="G29" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="b">
         <v>1</v>
@@ -1944,15 +4278,90 @@
         <v>1</v>
       </c>
       <c r="O29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P29" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>1</v>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+      <c r="W29" t="b">
+        <v>0</v>
+      </c>
+      <c r="X29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" t="n">
         <v>9</v>
@@ -1965,26 +4374,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>מעורבות/ תפקוד המשפחה</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="I30" t="n">
         <v>4</v>
       </c>
-      <c r="G30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
       <c r="J30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -1999,11 +4414,88 @@
         <v>0</v>
       </c>
       <c r="P30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>1</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="n">
+        <v>3</v>
+      </c>
       <c r="B31" t="n">
         <v>9</v>
       </c>
@@ -2015,23 +4507,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>בעיני - מציאת המענה למגבלה ( שירות , התאמת מסגרת)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="I31" t="n">
         <v>3</v>
       </c>
-      <c r="G31" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
       <c r="J31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -2040,15 +4538,90 @@
         <v>0</v>
       </c>
       <c r="M31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="b">
         <v>0</v>
       </c>
       <c r="P31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>1</v>
+      </c>
+      <c r="R31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" t="b">
+        <v>0</v>
+      </c>
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+      <c r="W31" t="b">
+        <v>0</v>
+      </c>
+      <c r="X31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2067,26 +4640,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="I32" t="n">
         <v>5</v>
       </c>
-      <c r="G32" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
       <c r="J32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -2095,12 +4674,87 @@
         <v>0</v>
       </c>
       <c r="N32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="b">
         <v>0</v>
       </c>
       <c r="P32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <v>0</v>
+      </c>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" t="b">
+        <v>0</v>
+      </c>
+      <c r="X32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2119,40 +4773,121 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>אותם הרכיבים כמו בתיק רגיל</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="I33" t="n">
         <v>5</v>
       </c>
-      <c r="G33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33" t="b">
-        <v>1</v>
-      </c>
       <c r="J33" t="b">
         <v>0</v>
       </c>
       <c r="K33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
       </c>
       <c r="O33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>1</v>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" t="b">
+        <v>0</v>
+      </c>
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33" t="b">
+        <v>0</v>
+      </c>
+      <c r="X33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2171,21 +4906,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מורכבות של מוגבלות ונפש </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="I34" t="n">
         <v>5</v>
       </c>
-      <c r="G34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
       <c r="J34" t="b">
         <v>0</v>
       </c>
@@ -2193,19 +4934,94 @@
         <v>1</v>
       </c>
       <c r="L34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
       </c>
       <c r="O34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>1</v>
+      </c>
+      <c r="R34" t="b">
+        <v>1</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="b">
+        <v>1</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" t="b">
+        <v>1</v>
+      </c>
+      <c r="W34" t="b">
+        <v>0</v>
+      </c>
+      <c r="X34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2223,41 +5039,122 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>זמינות שירותים הן ברמה מקומית והן אזורית. טיפול כולל בכל המשפחה ולא רק באדם עם מוגבלות</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="I35" t="n">
         <v>5</v>
       </c>
-      <c r="G35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
       <c r="J35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="b">
         <v>0</v>
       </c>
       <c r="N35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="b">
         <v>0</v>
       </c>
       <c r="P35" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+      <c r="V35" t="b">
+        <v>1</v>
+      </c>
+      <c r="W35" t="b">
+        <v>1</v>
+      </c>
+      <c r="X35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2275,32 +5172,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מחסור בכח אדם.ריבוי ועליה באבחונים אוטיזם.מחסור בעוס לחוק משה </t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="I36" t="n">
         <v>4</v>
       </c>
-      <c r="G36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
       <c r="J36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2309,12 +5212,87 @@
         <v>1</v>
       </c>
       <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="b">
+        <v>1</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+      <c r="V36" t="b">
+        <v>0</v>
+      </c>
+      <c r="W36" t="b">
+        <v>0</v>
+      </c>
+      <c r="X36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B37" t="n">
         <v>2</v>
@@ -2327,29 +5305,35 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הליווי</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="I37" t="n">
         <v>4</v>
       </c>
-      <c r="G37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="b">
         <v>1</v>
@@ -2358,15 +5342,90 @@
         <v>1</v>
       </c>
       <c r="O37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="b">
         <v>0</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" t="b">
+        <v>1</v>
+      </c>
+      <c r="V37" t="b">
+        <v>0</v>
+      </c>
+      <c r="W37" t="b">
+        <v>0</v>
+      </c>
+      <c r="X37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B38" t="n">
         <v>5</v>
@@ -2379,41 +5438,122 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הטיפול</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="I38" t="n">
         <v>4</v>
       </c>
-      <c r="G38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38" t="b">
-        <v>0</v>
-      </c>
       <c r="J38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
       </c>
       <c r="O38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>1</v>
+      </c>
+      <c r="R38" t="b">
+        <v>1</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+      <c r="V38" t="b">
+        <v>1</v>
+      </c>
+      <c r="W38" t="b">
+        <v>1</v>
+      </c>
+      <c r="X38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2431,29 +5571,35 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">אנטנסיביות הטיפול שיכול לנבוע ולהיות מושפע מכל אחד מהמשתנים האחריםד מהמשתנים </t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="I39" t="n">
         <v>5</v>
       </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="b">
         <v>1</v>
@@ -2462,15 +5608,90 @@
         <v>1</v>
       </c>
       <c r="O39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="b">
+        <v>0</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
+      </c>
+      <c r="V39" t="b">
+        <v>1</v>
+      </c>
+      <c r="W39" t="b">
+        <v>0</v>
+      </c>
+      <c r="X39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B40" t="n">
         <v>9</v>
@@ -2483,26 +5704,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>מעורבות/ תפקוד המשפחה</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="I40" t="n">
         <v>5</v>
       </c>
-      <c r="G40" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
       <c r="J40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -2517,11 +5744,88 @@
         <v>0</v>
       </c>
       <c r="P40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
+      <c r="R40" t="b">
+        <v>1</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="b">
+        <v>0</v>
+      </c>
+      <c r="U40" t="b">
+        <v>0</v>
+      </c>
+      <c r="V40" t="b">
+        <v>0</v>
+      </c>
+      <c r="W40" t="b">
+        <v>1</v>
+      </c>
+      <c r="X40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="n">
+        <v>3</v>
+      </c>
       <c r="B41" t="n">
         <v>9</v>
       </c>
@@ -2533,23 +5837,29 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>בעיני - מציאת המענה למגבלה ( שירות , התאמת מסגרת)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
         </is>
       </c>
-      <c r="F41" t="n">
+      <c r="I41" t="n">
         <v>3</v>
       </c>
-      <c r="G41" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -2558,15 +5868,90 @@
         <v>0</v>
       </c>
       <c r="M41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="b">
         <v>0</v>
       </c>
       <c r="P41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="b">
+        <v>1</v>
+      </c>
+      <c r="R41" t="b">
+        <v>1</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="b">
+        <v>0</v>
+      </c>
+      <c r="U41" t="b">
+        <v>0</v>
+      </c>
+      <c r="V41" t="b">
+        <v>1</v>
+      </c>
+      <c r="W41" t="b">
+        <v>0</v>
+      </c>
+      <c r="X41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2585,26 +5970,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="I42" t="n">
         <v>4</v>
       </c>
-      <c r="G42" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42" t="b">
-        <v>0</v>
-      </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
@@ -2613,12 +6004,87 @@
         <v>0</v>
       </c>
       <c r="N42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="b">
         <v>0</v>
       </c>
       <c r="P42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="b">
+        <v>0</v>
+      </c>
+      <c r="U42" t="b">
+        <v>0</v>
+      </c>
+      <c r="V42" t="b">
+        <v>0</v>
+      </c>
+      <c r="W42" t="b">
+        <v>0</v>
+      </c>
+      <c r="X42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2637,40 +6103,121 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>אותם הרכיבים כמו בתיק רגיל</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="I43" t="n">
         <v>5</v>
       </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
       </c>
       <c r="O43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="b">
+        <v>1</v>
+      </c>
+      <c r="R43" t="b">
+        <v>1</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="b">
+        <v>0</v>
+      </c>
+      <c r="U43" t="b">
+        <v>0</v>
+      </c>
+      <c r="V43" t="b">
+        <v>0</v>
+      </c>
+      <c r="W43" t="b">
+        <v>0</v>
+      </c>
+      <c r="X43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2689,21 +6236,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מורכבות של מוגבלות ונפש </t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="I44" t="n">
         <v>5</v>
       </c>
-      <c r="G44" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" t="b">
-        <v>1</v>
-      </c>
-      <c r="I44" t="b">
-        <v>0</v>
-      </c>
       <c r="J44" t="b">
         <v>0</v>
       </c>
@@ -2711,19 +6264,94 @@
         <v>1</v>
       </c>
       <c r="L44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
       </c>
       <c r="O44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
+      </c>
+      <c r="Q44" t="b">
+        <v>1</v>
+      </c>
+      <c r="R44" t="b">
+        <v>1</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="b">
+        <v>1</v>
+      </c>
+      <c r="U44" t="b">
+        <v>0</v>
+      </c>
+      <c r="V44" t="b">
+        <v>1</v>
+      </c>
+      <c r="W44" t="b">
+        <v>0</v>
+      </c>
+      <c r="X44" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO44" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2741,41 +6369,122 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>זמינות שירותים הן ברמה מקומית והן אזורית. טיפול כולל בכל המשפחה ולא רק באדם עם מוגבלות</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="I45" t="n">
         <v>5</v>
       </c>
-      <c r="G45" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
       <c r="J45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
       </c>
       <c r="N45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="b">
         <v>0</v>
       </c>
       <c r="P45" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="b">
+        <v>0</v>
+      </c>
+      <c r="U45" t="b">
+        <v>0</v>
+      </c>
+      <c r="V45" t="b">
+        <v>1</v>
+      </c>
+      <c r="W45" t="b">
+        <v>1</v>
+      </c>
+      <c r="X45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2793,32 +6502,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מחסור בכח אדם.ריבוי ועליה באבחונים אוטיזם.מחסור בעוס לחוק משה </t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
         </is>
       </c>
-      <c r="F46" t="n">
+      <c r="I46" t="n">
         <v>5</v>
       </c>
-      <c r="G46" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" t="b">
-        <v>0</v>
-      </c>
-      <c r="I46" t="b">
-        <v>0</v>
-      </c>
       <c r="J46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
@@ -2827,12 +6542,87 @@
         <v>1</v>
       </c>
       <c r="P46" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="b">
+        <v>1</v>
+      </c>
+      <c r="R46" t="b">
+        <v>1</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="b">
+        <v>0</v>
+      </c>
+      <c r="U46" t="b">
+        <v>0</v>
+      </c>
+      <c r="V46" t="b">
+        <v>0</v>
+      </c>
+      <c r="W46" t="b">
+        <v>0</v>
+      </c>
+      <c r="X46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO46" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B47" t="n">
         <v>2</v>
@@ -2845,29 +6635,35 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הליווי</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="I47" t="n">
         <v>5</v>
       </c>
-      <c r="G47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" t="b">
-        <v>1</v>
-      </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="b">
         <v>1</v>
@@ -2876,15 +6672,90 @@
         <v>1</v>
       </c>
       <c r="O47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="b">
         <v>0</v>
+      </c>
+      <c r="Q47" t="b">
+        <v>1</v>
+      </c>
+      <c r="R47" t="b">
+        <v>1</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="b">
+        <v>0</v>
+      </c>
+      <c r="U47" t="b">
+        <v>1</v>
+      </c>
+      <c r="V47" t="b">
+        <v>0</v>
+      </c>
+      <c r="W47" t="b">
+        <v>0</v>
+      </c>
+      <c r="X47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B48" t="n">
         <v>5</v>
@@ -2897,41 +6768,122 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הטיפול</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="I48" t="n">
         <v>4</v>
       </c>
-      <c r="G48" t="b">
-        <v>1</v>
-      </c>
-      <c r="H48" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
       <c r="J48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="b">
         <v>1</v>
       </c>
       <c r="O48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q48" t="b">
+        <v>1</v>
+      </c>
+      <c r="R48" t="b">
+        <v>1</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="b">
+        <v>0</v>
+      </c>
+      <c r="U48" t="b">
+        <v>0</v>
+      </c>
+      <c r="V48" t="b">
+        <v>1</v>
+      </c>
+      <c r="W48" t="b">
+        <v>1</v>
+      </c>
+      <c r="X48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO48" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2949,29 +6901,35 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">אנטנסיביות הטיפול שיכול לנבוע ולהיות מושפע מכל אחד מהמשתנים האחריםד מהמשתנים </t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="I49" t="n">
         <v>5</v>
       </c>
-      <c r="G49" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49" t="b">
-        <v>0</v>
-      </c>
       <c r="J49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="b">
         <v>1</v>
@@ -2980,15 +6938,90 @@
         <v>1</v>
       </c>
       <c r="O49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q49" t="b">
+        <v>1</v>
+      </c>
+      <c r="R49" t="b">
+        <v>1</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="b">
+        <v>0</v>
+      </c>
+      <c r="U49" t="b">
+        <v>0</v>
+      </c>
+      <c r="V49" t="b">
+        <v>1</v>
+      </c>
+      <c r="W49" t="b">
+        <v>0</v>
+      </c>
+      <c r="X49" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B50" t="n">
         <v>9</v>
@@ -3001,26 +7034,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>מעורבות/ תפקוד המשפחה</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="I50" t="n">
         <v>5</v>
       </c>
-      <c r="G50" t="b">
-        <v>1</v>
-      </c>
-      <c r="H50" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" t="b">
-        <v>0</v>
-      </c>
       <c r="J50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -3035,11 +7074,88 @@
         <v>0</v>
       </c>
       <c r="P50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="b">
+        <v>0</v>
+      </c>
+      <c r="R50" t="b">
+        <v>1</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="b">
+        <v>0</v>
+      </c>
+      <c r="U50" t="b">
+        <v>0</v>
+      </c>
+      <c r="V50" t="b">
+        <v>0</v>
+      </c>
+      <c r="W50" t="b">
+        <v>1</v>
+      </c>
+      <c r="X50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="n">
+        <v>3</v>
+      </c>
       <c r="B51" t="n">
         <v>9</v>
       </c>
@@ -3051,23 +7167,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>בעיני - מציאת המענה למגבלה ( שירות , התאמת מסגרת)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="I51" t="n">
         <v>4</v>
       </c>
-      <c r="G51" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" t="b">
-        <v>0</v>
-      </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -3076,15 +7198,90 @@
         <v>0</v>
       </c>
       <c r="M51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="b">
         <v>0</v>
       </c>
       <c r="P51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="b">
+        <v>1</v>
+      </c>
+      <c r="R51" t="b">
+        <v>1</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="b">
+        <v>0</v>
+      </c>
+      <c r="U51" t="b">
+        <v>0</v>
+      </c>
+      <c r="V51" t="b">
+        <v>1</v>
+      </c>
+      <c r="W51" t="b">
+        <v>0</v>
+      </c>
+      <c r="X51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3103,26 +7300,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="I52" t="n">
         <v>4</v>
       </c>
-      <c r="G52" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" t="b">
-        <v>0</v>
-      </c>
-      <c r="I52" t="b">
-        <v>0</v>
-      </c>
       <c r="J52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -3131,12 +7334,87 @@
         <v>0</v>
       </c>
       <c r="N52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="b">
         <v>0</v>
       </c>
       <c r="P52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="b">
+        <v>0</v>
+      </c>
+      <c r="R52" t="b">
+        <v>0</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="b">
+        <v>0</v>
+      </c>
+      <c r="U52" t="b">
+        <v>0</v>
+      </c>
+      <c r="V52" t="b">
+        <v>0</v>
+      </c>
+      <c r="W52" t="b">
+        <v>0</v>
+      </c>
+      <c r="X52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3155,40 +7433,121 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>אותם הרכיבים כמו בתיק רגיל</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="I53" t="n">
         <v>3</v>
       </c>
-      <c r="G53" t="b">
-        <v>0</v>
-      </c>
-      <c r="H53" t="b">
-        <v>0</v>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
       <c r="K53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
       </c>
       <c r="O53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="b">
+        <v>1</v>
+      </c>
+      <c r="R53" t="b">
+        <v>1</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="b">
+        <v>0</v>
+      </c>
+      <c r="U53" t="b">
+        <v>0</v>
+      </c>
+      <c r="V53" t="b">
+        <v>0</v>
+      </c>
+      <c r="W53" t="b">
+        <v>0</v>
+      </c>
+      <c r="X53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3207,21 +7566,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מורכבות של מוגבלות ונפש </t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
         </is>
       </c>
-      <c r="F54" t="n">
+      <c r="I54" t="n">
         <v>4</v>
       </c>
-      <c r="G54" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" t="b">
-        <v>1</v>
-      </c>
-      <c r="I54" t="b">
-        <v>0</v>
-      </c>
       <c r="J54" t="b">
         <v>0</v>
       </c>
@@ -3229,19 +7594,94 @@
         <v>1</v>
       </c>
       <c r="L54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="b">
         <v>1</v>
       </c>
       <c r="O54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
+      </c>
+      <c r="Q54" t="b">
+        <v>1</v>
+      </c>
+      <c r="R54" t="b">
+        <v>1</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="b">
+        <v>1</v>
+      </c>
+      <c r="U54" t="b">
+        <v>0</v>
+      </c>
+      <c r="V54" t="b">
+        <v>1</v>
+      </c>
+      <c r="W54" t="b">
+        <v>0</v>
+      </c>
+      <c r="X54" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO54" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3259,41 +7699,122 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>זמינות שירותים הן ברמה מקומית והן אזורית. טיפול כולל בכל המשפחה ולא רק באדם עם מוגבלות</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
         </is>
       </c>
-      <c r="F55" t="n">
+      <c r="I55" t="n">
         <v>5</v>
       </c>
-      <c r="G55" t="b">
-        <v>1</v>
-      </c>
-      <c r="H55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I55" t="b">
-        <v>0</v>
-      </c>
       <c r="J55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="b">
         <v>0</v>
       </c>
       <c r="N55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="b">
         <v>0</v>
       </c>
       <c r="P55" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q55" t="b">
+        <v>0</v>
+      </c>
+      <c r="R55" t="b">
+        <v>0</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="b">
+        <v>0</v>
+      </c>
+      <c r="U55" t="b">
+        <v>0</v>
+      </c>
+      <c r="V55" t="b">
+        <v>1</v>
+      </c>
+      <c r="W55" t="b">
+        <v>1</v>
+      </c>
+      <c r="X55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3311,32 +7832,38 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">מחסור בכח אדם.ריבוי ועליה באבחונים אוטיזם.מחסור בעוס לחוק משה </t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
         </is>
       </c>
-      <c r="F56" t="n">
+      <c r="I56" t="n">
         <v>5</v>
       </c>
-      <c r="G56" t="b">
-        <v>1</v>
-      </c>
-      <c r="H56" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56" t="b">
-        <v>0</v>
-      </c>
       <c r="J56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="b">
         <v>1</v>
@@ -3345,12 +7872,87 @@
         <v>1</v>
       </c>
       <c r="P56" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="b">
+        <v>1</v>
+      </c>
+      <c r="R56" t="b">
+        <v>1</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="b">
+        <v>0</v>
+      </c>
+      <c r="U56" t="b">
+        <v>0</v>
+      </c>
+      <c r="V56" t="b">
+        <v>0</v>
+      </c>
+      <c r="W56" t="b">
+        <v>0</v>
+      </c>
+      <c r="X56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO56" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B57" t="n">
         <v>2</v>
@@ -3363,29 +7965,35 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הליווי</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
           <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="I57" t="n">
         <v>4</v>
       </c>
-      <c r="G57" t="b">
-        <v>1</v>
-      </c>
-      <c r="H57" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="b">
         <v>1</v>
@@ -3394,15 +8002,90 @@
         <v>1</v>
       </c>
       <c r="O57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" t="b">
         <v>0</v>
+      </c>
+      <c r="Q57" t="b">
+        <v>1</v>
+      </c>
+      <c r="R57" t="b">
+        <v>1</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="b">
+        <v>0</v>
+      </c>
+      <c r="U57" t="b">
+        <v>1</v>
+      </c>
+      <c r="V57" t="b">
+        <v>0</v>
+      </c>
+      <c r="W57" t="b">
+        <v>0</v>
+      </c>
+      <c r="X57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B58" t="n">
         <v>5</v>
@@ -3415,41 +8098,122 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>אינטנסיביות הטיפול</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
           <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="I58" t="n">
         <v>4</v>
       </c>
-      <c r="G58" t="b">
-        <v>1</v>
-      </c>
-      <c r="H58" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58" t="b">
-        <v>0</v>
-      </c>
       <c r="J58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
       </c>
       <c r="O58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P58" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q58" t="b">
+        <v>1</v>
+      </c>
+      <c r="R58" t="b">
+        <v>1</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="b">
+        <v>0</v>
+      </c>
+      <c r="U58" t="b">
+        <v>0</v>
+      </c>
+      <c r="V58" t="b">
+        <v>1</v>
+      </c>
+      <c r="W58" t="b">
+        <v>1</v>
+      </c>
+      <c r="X58" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y58" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN58" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO58" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3467,29 +8231,35 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">אנטנסיביות הטיפול שיכול לנבוע ולהיות מושפע מכל אחד מהמשתנים האחריםד מהמשתנים </t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
         </is>
       </c>
-      <c r="F59" t="n">
+      <c r="I59" t="n">
         <v>4</v>
       </c>
-      <c r="G59" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
       <c r="J59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" t="b">
         <v>1</v>
@@ -3498,15 +8268,90 @@
         <v>1</v>
       </c>
       <c r="O59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q59" t="b">
+        <v>1</v>
+      </c>
+      <c r="R59" t="b">
+        <v>1</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="b">
+        <v>0</v>
+      </c>
+      <c r="U59" t="b">
+        <v>0</v>
+      </c>
+      <c r="V59" t="b">
+        <v>1</v>
+      </c>
+      <c r="W59" t="b">
+        <v>0</v>
+      </c>
+      <c r="X59" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y59" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO59" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B60" t="n">
         <v>9</v>
@@ -3519,26 +8364,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>מעורבות/ תפקוד המשפחה</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
           <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
         </is>
       </c>
-      <c r="F60" t="n">
+      <c r="I60" t="n">
         <v>5</v>
       </c>
-      <c r="G60" t="b">
-        <v>1</v>
-      </c>
-      <c r="H60" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60" t="b">
-        <v>0</v>
-      </c>
       <c r="J60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -3553,11 +8404,88 @@
         <v>0</v>
       </c>
       <c r="P60" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="b">
+        <v>0</v>
+      </c>
+      <c r="R60" t="b">
+        <v>1</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="b">
+        <v>0</v>
+      </c>
+      <c r="U60" t="b">
+        <v>0</v>
+      </c>
+      <c r="V60" t="b">
+        <v>0</v>
+      </c>
+      <c r="W60" t="b">
+        <v>1</v>
+      </c>
+      <c r="X60" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM60" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="n">
+        <v>3</v>
+      </c>
       <c r="B61" t="n">
         <v>9</v>
       </c>
@@ -3569,23 +8497,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>בעיני - מציאת המענה למגבלה ( שירות , התאמת מסגרת)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
           <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
         </is>
       </c>
-      <c r="F61" t="n">
+      <c r="I61" t="n">
         <v>4</v>
       </c>
-      <c r="G61" t="b">
-        <v>1</v>
-      </c>
-      <c r="H61" t="b">
-        <v>0</v>
-      </c>
-      <c r="I61" t="b">
-        <v>0</v>
-      </c>
       <c r="J61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="b">
         <v>0</v>
@@ -3594,15 +8528,90 @@
         <v>0</v>
       </c>
       <c r="M61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="b">
         <v>0</v>
       </c>
       <c r="P61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="b">
+        <v>1</v>
+      </c>
+      <c r="R61" t="b">
+        <v>1</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="b">
+        <v>0</v>
+      </c>
+      <c r="U61" t="b">
+        <v>0</v>
+      </c>
+      <c r="V61" t="b">
+        <v>1</v>
+      </c>
+      <c r="W61" t="b">
+        <v>0</v>
+      </c>
+      <c r="X61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL61" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO61" t="b">
         <v>0</v>
       </c>
     </row>

--- a/survey_encoded.xlsx
+++ b/survey_encoded.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO61"/>
+  <dimension ref="A1:AN61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,135 +501,130 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>משתנים נוספים לעומס במוגבלויות_רמת תפקוד של האדם, מעורבות/תפקוד המשפחה, אינטנסיביות הליווי, תיאום בין־מערכתי</t>
+          <t>תחומי העומס_אזרחים ותיקים</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>תחומי העומס_אזרחים ותיקים</t>
+          <t>תחומי העומס_חוק סדרי דין</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>תחומי העומס_חוק סדרי דין</t>
+          <t>תחומי העומס_חוק נוער</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>תחומי העומס_חוק נוער</t>
+          <t>תחומי העומס_משפחה</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>תחומי העומס_משפחה</t>
+          <t>תחומי העומס_תחום נוער וצעירים</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>תחומי העומס_תחום נוער וצעירים</t>
+          <t>משתנים נוספים לעומס במוגבלויות_טיפול לבני משפחה</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>משתנים נוספים לעומס במוגבלויות_טיפול לבני משפחה</t>
+          <t>משתנים נוספים לעומס במוגבלויות_זמינות שירותים</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>משתנים נוספים לעומס במוגבלויות_זמינות שירותים</t>
+          <t>משתנים נוספים לעומס במוגבלויות_מורכבות המוגבלות</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>משתנים נוספים לעומס במוגבלויות_מורכבות המוגבלות</t>
+          <t>משתנים נוספים לעומס במוגבלויות_מעורבות/תפקוד המשפחה</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>משתנים נוספים לעומס במוגבלויות_מעורבות/תפקוד המשפחה</t>
+          <t>משתנים נוספים לעומס במוגבלויות_רמת תפקוד</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>משתנים נוספים לעומס במוגבלויות_רמת תפקוד</t>
+          <t>היבט נוסף במוגבלויות_מגוון השירותים שמקבל האדם</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>היבט נוסף במוגבלויות_מגוון השירותים שמקבל האדם</t>
+          <t>היבט נוסף במוגבלויות_הוצאה חוץ ביתית</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>היבט נוסף במוגבלויות_הוצאה חוץ ביתית</t>
+          <t>היבט נוסף במוגבלויות_מעורבות עם בריאות הנפש</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>היבט נוסף במוגבלויות_מעורבות עם בריאות הנפש</t>
+          <t>היבט נוסף במוגבלויות_מציאת מסגרת חינוכית</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>היבט נוסף במוגבלויות_מציאת מסגרת חינוכית</t>
+          <t>היבט נוסף במוגבלויות_בירוקרטיה</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>היבט נוסף במוגבלויות_בירוקרטיה</t>
+          <t>היבט נוסף במוגבלויות_הביקורים במסגרות</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>היבט נוסף במוגבלויות_הביקורים במסגרות</t>
+          <t>היבט נוסף במוגבלויות_הכשרה והתמקצעות</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>היבט נוסף במוגבלויות_הכשרה והתמקצעות</t>
+          <t>משתנים נוספים לעומס באזרחים ותיקים_עורף משפחתי</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>משתנים נוספים לעומס באזרחים ותיקים_עורף משפחתי</t>
+          <t>משתנים נוספים לעומס באזרחים ותיקים_קשר ופיקוח במסגרות</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>משתנים נוספים לעומס באזרחים ותיקים_קשר ופיקוח במסגרות</t>
+          <t>משתנים נוספים לעומס באזרחים ותיקים_טיפול לבני משפחה</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>משתנים נוספים לעומס באזרחים ותיקים_טיפול לבני משפחה</t>
+          <t>משתנים נוספים לעומס באזרחים ותיקים_מענה בקהילה האזרחית</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>משתנים נוספים לעומס באזרחים ותיקים_מענה בקהילה האזרחית</t>
+          <t>תחומים עם פער_חוק נוער</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>תחומים עם פער_חוק נוער</t>
+          <t>תחומים עם פער_חוק סדרי דין</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>תחומים עם פער_חוק סדרי דין</t>
+          <t>תחומים עם פער_מוגבלויות</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>תחומים עם פער_מוגבלויות</t>
+          <t>תחומים עם פער_אזרחים ותיקים</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>תחומים עם פער_אזרחים ותיקים</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>תחומים עם פער_משפחה</t>
         </is>
@@ -756,15 +751,12 @@
         <v>0</v>
       </c>
       <c r="AL2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -823,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="b">
         <v>1</v>
@@ -832,7 +824,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -895,9 +887,6 @@
         <v>0</v>
       </c>
       <c r="AN3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -953,7 +942,7 @@
         <v>1</v>
       </c>
       <c r="O4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
@@ -968,19 +957,19 @@
         <v>1</v>
       </c>
       <c r="T4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="b">
         <v>0</v>
@@ -989,13 +978,13 @@
         <v>0</v>
       </c>
       <c r="AA4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="b">
         <v>1</v>
       </c>
       <c r="AC4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
@@ -1016,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="b">
         <v>1</v>
@@ -1028,9 +1017,6 @@
         <v>1</v>
       </c>
       <c r="AN4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1086,10 +1072,10 @@
         <v>1</v>
       </c>
       <c r="O5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -1104,13 +1090,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="b">
         <v>1</v>
       </c>
       <c r="W5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="b">
         <v>0</v>
@@ -1131,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="b">
         <v>0</v>
@@ -1155,15 +1141,12 @@
         <v>0</v>
       </c>
       <c r="AL5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="b">
         <v>1</v>
       </c>
       <c r="AN5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1231,7 +1214,7 @@
         <v>1</v>
       </c>
       <c r="S6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -1243,10 +1226,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
@@ -1267,13 +1250,13 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="b">
         <v>1</v>
       </c>
       <c r="AG6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="b">
         <v>0</v>
@@ -1288,15 +1271,12 @@
         <v>0</v>
       </c>
       <c r="AL6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="b">
         <v>1</v>
       </c>
       <c r="AN6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1355,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="b">
         <v>1</v>
@@ -1364,13 +1344,13 @@
         <v>1</v>
       </c>
       <c r="S7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="b">
         <v>0</v>
@@ -1394,10 +1374,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
@@ -1409,10 +1389,10 @@
         <v>0</v>
       </c>
       <c r="AH7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="b">
         <v>0</v>
@@ -1421,15 +1401,12 @@
         <v>0</v>
       </c>
       <c r="AL7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1485,7 +1462,7 @@
         <v>1</v>
       </c>
       <c r="O8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="b">
         <v>1</v>
@@ -1497,25 +1474,25 @@
         <v>1</v>
       </c>
       <c r="S8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
@@ -1539,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -1554,15 +1531,12 @@
         <v>0</v>
       </c>
       <c r="AL8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="b">
         <v>1</v>
       </c>
       <c r="AN8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1618,7 +1592,7 @@
         <v>1</v>
       </c>
       <c r="O9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="b">
         <v>1</v>
@@ -1630,28 +1604,28 @@
         <v>1</v>
       </c>
       <c r="S9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
       <c r="Y9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -1678,24 +1652,21 @@
         <v>0</v>
       </c>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="b">
         <v>1</v>
       </c>
       <c r="AM9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1757,10 +1728,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -1772,10 +1743,10 @@
         <v>0</v>
       </c>
       <c r="V10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="b">
         <v>0</v>
@@ -1784,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="Z10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="b">
         <v>0</v>
@@ -1802,10 +1773,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="b">
         <v>0</v>
@@ -1820,15 +1791,12 @@
         <v>0</v>
       </c>
       <c r="AL10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1887,13 +1855,13 @@
         <v>0</v>
       </c>
       <c r="P11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
       </c>
       <c r="R11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
@@ -1902,10 +1870,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="b">
         <v>0</v>
@@ -1917,10 +1885,10 @@
         <v>0</v>
       </c>
       <c r="Z11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="b">
         <v>0</v>
@@ -1947,21 +1915,18 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="b">
         <v>1</v>
       </c>
       <c r="AL11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="b">
         <v>0</v>
       </c>
       <c r="AN11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2086,15 +2051,12 @@
         <v>0</v>
       </c>
       <c r="AL12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2153,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
@@ -2162,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="S13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="b">
         <v>0</v>
@@ -2225,9 +2187,6 @@
         <v>0</v>
       </c>
       <c r="AN13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2283,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="O14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="b">
         <v>1</v>
@@ -2298,19 +2257,19 @@
         <v>1</v>
       </c>
       <c r="T14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="b">
         <v>0</v>
@@ -2319,13 +2278,13 @@
         <v>0</v>
       </c>
       <c r="AA14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="b">
         <v>1</v>
       </c>
       <c r="AC14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
@@ -2346,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK14" t="b">
         <v>1</v>
@@ -2358,9 +2317,6 @@
         <v>1</v>
       </c>
       <c r="AN14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2416,10 +2372,10 @@
         <v>1</v>
       </c>
       <c r="O15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -2434,13 +2390,13 @@
         <v>0</v>
       </c>
       <c r="U15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="b">
         <v>1</v>
       </c>
       <c r="W15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="b">
         <v>0</v>
@@ -2461,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="AD15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="b">
         <v>0</v>
@@ -2485,15 +2441,12 @@
         <v>0</v>
       </c>
       <c r="AL15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM15" t="b">
         <v>1</v>
       </c>
       <c r="AN15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2561,7 +2514,7 @@
         <v>1</v>
       </c>
       <c r="S16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="b">
         <v>0</v>
@@ -2573,10 +2526,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="b">
         <v>0</v>
@@ -2597,13 +2550,13 @@
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="b">
         <v>1</v>
       </c>
       <c r="AG16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="b">
         <v>0</v>
@@ -2618,15 +2571,12 @@
         <v>0</v>
       </c>
       <c r="AL16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM16" t="b">
         <v>1</v>
       </c>
       <c r="AN16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2685,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
@@ -2694,13 +2644,13 @@
         <v>1</v>
       </c>
       <c r="S17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="b">
         <v>0</v>
@@ -2724,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
@@ -2739,10 +2689,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="b">
         <v>0</v>
@@ -2751,15 +2701,12 @@
         <v>0</v>
       </c>
       <c r="AL17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2815,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" t="b">
         <v>1</v>
@@ -2827,25 +2774,25 @@
         <v>1</v>
       </c>
       <c r="S18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="b">
         <v>0</v>
       </c>
       <c r="U18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="b">
         <v>1</v>
       </c>
       <c r="W18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="b">
         <v>0</v>
@@ -2869,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="b">
         <v>0</v>
@@ -2884,15 +2831,12 @@
         <v>0</v>
       </c>
       <c r="AL18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM18" t="b">
         <v>1</v>
       </c>
       <c r="AN18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2948,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="O19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="b">
         <v>1</v>
@@ -2960,28 +2904,28 @@
         <v>1</v>
       </c>
       <c r="S19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="b">
         <v>0</v>
       </c>
       <c r="U19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
       <c r="Y19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="b">
         <v>0</v>
@@ -3008,24 +2952,21 @@
         <v>0</v>
       </c>
       <c r="AI19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL19" t="b">
         <v>1</v>
       </c>
       <c r="AM19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3087,10 +3028,10 @@
         <v>0</v>
       </c>
       <c r="Q20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -3102,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="b">
         <v>0</v>
@@ -3114,10 +3055,10 @@
         <v>0</v>
       </c>
       <c r="Z20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="b">
         <v>0</v>
@@ -3132,10 +3073,10 @@
         <v>0</v>
       </c>
       <c r="AF20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="b">
         <v>0</v>
@@ -3150,15 +3091,12 @@
         <v>0</v>
       </c>
       <c r="AL20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3217,13 +3155,13 @@
         <v>0</v>
       </c>
       <c r="P21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="b">
         <v>0</v>
@@ -3232,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="U21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="b">
         <v>0</v>
@@ -3247,10 +3185,10 @@
         <v>0</v>
       </c>
       <c r="Z21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="b">
         <v>0</v>
@@ -3277,21 +3215,18 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK21" t="b">
         <v>1</v>
       </c>
       <c r="AL21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="b">
         <v>0</v>
       </c>
       <c r="AN21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3416,15 +3351,12 @@
         <v>0</v>
       </c>
       <c r="AL22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3483,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
@@ -3492,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="S23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="b">
         <v>0</v>
@@ -3555,9 +3487,6 @@
         <v>0</v>
       </c>
       <c r="AN23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3613,7 +3542,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="b">
         <v>1</v>
@@ -3628,19 +3557,19 @@
         <v>1</v>
       </c>
       <c r="T24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="b">
         <v>0</v>
@@ -3649,13 +3578,13 @@
         <v>0</v>
       </c>
       <c r="AA24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="b">
         <v>1</v>
       </c>
       <c r="AC24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="b">
         <v>0</v>
@@ -3676,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK24" t="b">
         <v>1</v>
@@ -3688,9 +3617,6 @@
         <v>1</v>
       </c>
       <c r="AN24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3746,10 +3672,10 @@
         <v>1</v>
       </c>
       <c r="O25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -3764,13 +3690,13 @@
         <v>0</v>
       </c>
       <c r="U25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="b">
         <v>1</v>
       </c>
       <c r="W25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X25" t="b">
         <v>0</v>
@@ -3791,10 +3717,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="b">
         <v>0</v>
@@ -3815,15 +3741,12 @@
         <v>0</v>
       </c>
       <c r="AL25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="b">
         <v>1</v>
       </c>
       <c r="AN25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO25" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3891,7 +3814,7 @@
         <v>1</v>
       </c>
       <c r="S26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="b">
         <v>0</v>
@@ -3903,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="b">
         <v>0</v>
@@ -3927,13 +3850,13 @@
         <v>0</v>
       </c>
       <c r="AE26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="b">
         <v>1</v>
       </c>
       <c r="AG26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="b">
         <v>0</v>
@@ -3948,15 +3871,12 @@
         <v>0</v>
       </c>
       <c r="AL26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="b">
         <v>1</v>
       </c>
       <c r="AN26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4015,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="b">
         <v>1</v>
@@ -4024,13 +3944,13 @@
         <v>1</v>
       </c>
       <c r="S27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="b">
         <v>0</v>
@@ -4054,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
@@ -4069,10 +3989,10 @@
         <v>0</v>
       </c>
       <c r="AH27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="b">
         <v>0</v>
@@ -4081,15 +4001,12 @@
         <v>0</v>
       </c>
       <c r="AL27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4145,7 +4062,7 @@
         <v>1</v>
       </c>
       <c r="O28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="b">
         <v>1</v>
@@ -4157,25 +4074,25 @@
         <v>1</v>
       </c>
       <c r="S28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="b">
         <v>0</v>
       </c>
       <c r="U28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="b">
         <v>1</v>
       </c>
       <c r="W28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="b">
         <v>0</v>
@@ -4199,10 +4116,10 @@
         <v>0</v>
       </c>
       <c r="AG28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4214,15 +4131,12 @@
         <v>0</v>
       </c>
       <c r="AL28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM28" t="b">
         <v>1</v>
       </c>
       <c r="AN28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO28" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4278,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="O29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" t="b">
         <v>1</v>
@@ -4290,28 +4204,28 @@
         <v>1</v>
       </c>
       <c r="S29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="b">
         <v>0</v>
       </c>
       <c r="U29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" t="b">
         <v>1</v>
       </c>
       <c r="Y29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="b">
         <v>0</v>
@@ -4338,24 +4252,21 @@
         <v>0</v>
       </c>
       <c r="AI29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL29" t="b">
         <v>1</v>
       </c>
       <c r="AM29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4417,10 +4328,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="b">
         <v>0</v>
@@ -4432,10 +4343,10 @@
         <v>0</v>
       </c>
       <c r="V30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="b">
         <v>0</v>
@@ -4444,10 +4355,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="b">
         <v>0</v>
@@ -4462,10 +4373,10 @@
         <v>0</v>
       </c>
       <c r="AF30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="b">
         <v>0</v>
@@ -4480,15 +4391,12 @@
         <v>0</v>
       </c>
       <c r="AL30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4547,13 +4455,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
       </c>
       <c r="R31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="b">
         <v>0</v>
@@ -4562,10 +4470,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" t="b">
         <v>0</v>
@@ -4577,10 +4485,10 @@
         <v>0</v>
       </c>
       <c r="Z31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="b">
         <v>0</v>
@@ -4607,21 +4515,18 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK31" t="b">
         <v>1</v>
       </c>
       <c r="AL31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="b">
         <v>0</v>
       </c>
       <c r="AN31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4746,15 +4651,12 @@
         <v>0</v>
       </c>
       <c r="AL32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4813,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="b">
         <v>1</v>
@@ -4822,7 +4724,7 @@
         <v>1</v>
       </c>
       <c r="S33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="b">
         <v>0</v>
@@ -4885,9 +4787,6 @@
         <v>0</v>
       </c>
       <c r="AN33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4943,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="O34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" t="b">
         <v>1</v>
@@ -4958,19 +4857,19 @@
         <v>1</v>
       </c>
       <c r="T34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="b">
         <v>0</v>
@@ -4979,13 +4878,13 @@
         <v>0</v>
       </c>
       <c r="AA34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="b">
         <v>1</v>
       </c>
       <c r="AC34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
@@ -5006,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK34" t="b">
         <v>1</v>
@@ -5018,9 +4917,6 @@
         <v>1</v>
       </c>
       <c r="AN34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5076,10 +4972,10 @@
         <v>1</v>
       </c>
       <c r="O35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="b">
         <v>0</v>
@@ -5094,13 +4990,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" t="b">
         <v>1</v>
       </c>
       <c r="W35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="b">
         <v>0</v>
@@ -5121,10 +5017,10 @@
         <v>0</v>
       </c>
       <c r="AD35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="b">
         <v>0</v>
@@ -5145,15 +5041,12 @@
         <v>0</v>
       </c>
       <c r="AL35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="b">
         <v>1</v>
       </c>
       <c r="AN35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO35" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5221,7 +5114,7 @@
         <v>1</v>
       </c>
       <c r="S36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="b">
         <v>0</v>
@@ -5233,10 +5126,10 @@
         <v>0</v>
       </c>
       <c r="W36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="b">
         <v>0</v>
@@ -5257,13 +5150,13 @@
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="b">
         <v>1</v>
       </c>
       <c r="AG36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="b">
         <v>0</v>
@@ -5278,15 +5171,12 @@
         <v>0</v>
       </c>
       <c r="AL36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM36" t="b">
         <v>1</v>
       </c>
       <c r="AN36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5345,7 +5235,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="b">
         <v>1</v>
@@ -5354,13 +5244,13 @@
         <v>1</v>
       </c>
       <c r="S37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" t="b">
         <v>0</v>
@@ -5384,10 +5274,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
@@ -5399,10 +5289,10 @@
         <v>0</v>
       </c>
       <c r="AH37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="b">
         <v>0</v>
@@ -5411,15 +5301,12 @@
         <v>0</v>
       </c>
       <c r="AL37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5475,7 +5362,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" t="b">
         <v>1</v>
@@ -5487,25 +5374,25 @@
         <v>1</v>
       </c>
       <c r="S38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="b">
         <v>0</v>
       </c>
       <c r="U38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" t="b">
         <v>1</v>
       </c>
       <c r="W38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="b">
         <v>0</v>
@@ -5529,10 +5416,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5544,15 +5431,12 @@
         <v>0</v>
       </c>
       <c r="AL38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM38" t="b">
         <v>1</v>
       </c>
       <c r="AN38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5608,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="O39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" t="b">
         <v>1</v>
@@ -5620,28 +5504,28 @@
         <v>1</v>
       </c>
       <c r="S39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" t="b">
         <v>0</v>
       </c>
       <c r="U39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="b">
         <v>1</v>
       </c>
       <c r="Y39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -5668,24 +5552,21 @@
         <v>0</v>
       </c>
       <c r="AI39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL39" t="b">
         <v>1</v>
       </c>
       <c r="AM39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5747,10 +5628,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -5762,10 +5643,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" t="b">
         <v>0</v>
@@ -5774,10 +5655,10 @@
         <v>0</v>
       </c>
       <c r="Z40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="b">
         <v>0</v>
@@ -5792,10 +5673,10 @@
         <v>0</v>
       </c>
       <c r="AF40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="b">
         <v>0</v>
@@ -5810,15 +5691,12 @@
         <v>0</v>
       </c>
       <c r="AL40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5877,13 +5755,13 @@
         <v>0</v>
       </c>
       <c r="P41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="b">
         <v>1</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="b">
         <v>0</v>
@@ -5892,10 +5770,10 @@
         <v>0</v>
       </c>
       <c r="U41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="b">
         <v>0</v>
@@ -5907,10 +5785,10 @@
         <v>0</v>
       </c>
       <c r="Z41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="b">
         <v>0</v>
@@ -5937,21 +5815,18 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK41" t="b">
         <v>1</v>
       </c>
       <c r="AL41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="b">
         <v>0</v>
       </c>
       <c r="AN41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6076,15 +5951,12 @@
         <v>0</v>
       </c>
       <c r="AL42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6143,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="b">
         <v>1</v>
@@ -6152,7 +6024,7 @@
         <v>1</v>
       </c>
       <c r="S43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43" t="b">
         <v>0</v>
@@ -6215,9 +6087,6 @@
         <v>0</v>
       </c>
       <c r="AN43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO43" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6273,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="O44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" t="b">
         <v>1</v>
@@ -6288,19 +6157,19 @@
         <v>1</v>
       </c>
       <c r="T44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="b">
         <v>0</v>
@@ -6309,13 +6178,13 @@
         <v>0</v>
       </c>
       <c r="AA44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="b">
         <v>1</v>
       </c>
       <c r="AC44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
@@ -6336,7 +6205,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK44" t="b">
         <v>1</v>
@@ -6348,9 +6217,6 @@
         <v>1</v>
       </c>
       <c r="AN44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6406,10 +6272,10 @@
         <v>1</v>
       </c>
       <c r="O45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
@@ -6424,13 +6290,13 @@
         <v>0</v>
       </c>
       <c r="U45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" t="b">
         <v>1</v>
       </c>
       <c r="W45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" t="b">
         <v>0</v>
@@ -6451,10 +6317,10 @@
         <v>0</v>
       </c>
       <c r="AD45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="b">
         <v>0</v>
@@ -6475,15 +6341,12 @@
         <v>0</v>
       </c>
       <c r="AL45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM45" t="b">
         <v>1</v>
       </c>
       <c r="AN45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO45" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6551,7 +6414,7 @@
         <v>1</v>
       </c>
       <c r="S46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="b">
         <v>0</v>
@@ -6563,10 +6426,10 @@
         <v>0</v>
       </c>
       <c r="W46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="b">
         <v>0</v>
@@ -6587,13 +6450,13 @@
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF46" t="b">
         <v>1</v>
       </c>
       <c r="AG46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="b">
         <v>0</v>
@@ -6608,15 +6471,12 @@
         <v>0</v>
       </c>
       <c r="AL46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM46" t="b">
         <v>1</v>
       </c>
       <c r="AN46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6675,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="b">
         <v>1</v>
@@ -6684,13 +6544,13 @@
         <v>1</v>
       </c>
       <c r="S47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" t="b">
         <v>0</v>
@@ -6714,10 +6574,10 @@
         <v>0</v>
       </c>
       <c r="AC47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
@@ -6729,10 +6589,10 @@
         <v>0</v>
       </c>
       <c r="AH47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="b">
         <v>0</v>
@@ -6741,15 +6601,12 @@
         <v>0</v>
       </c>
       <c r="AL47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6805,7 +6662,7 @@
         <v>1</v>
       </c>
       <c r="O48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" t="b">
         <v>1</v>
@@ -6817,25 +6674,25 @@
         <v>1</v>
       </c>
       <c r="S48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="b">
         <v>0</v>
       </c>
       <c r="U48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" t="b">
         <v>1</v>
       </c>
       <c r="W48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="b">
         <v>0</v>
@@ -6859,10 +6716,10 @@
         <v>0</v>
       </c>
       <c r="AG48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -6874,15 +6731,12 @@
         <v>0</v>
       </c>
       <c r="AL48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM48" t="b">
         <v>1</v>
       </c>
       <c r="AN48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO48" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6938,7 +6792,7 @@
         <v>1</v>
       </c>
       <c r="O49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" t="b">
         <v>1</v>
@@ -6950,28 +6804,28 @@
         <v>1</v>
       </c>
       <c r="S49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" t="b">
         <v>0</v>
       </c>
       <c r="U49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X49" t="b">
         <v>1</v>
       </c>
       <c r="Y49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="b">
         <v>0</v>
@@ -6998,24 +6852,21 @@
         <v>0</v>
       </c>
       <c r="AI49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL49" t="b">
         <v>1</v>
       </c>
       <c r="AM49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7077,10 +6928,10 @@
         <v>0</v>
       </c>
       <c r="Q50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="b">
         <v>0</v>
@@ -7092,10 +6943,10 @@
         <v>0</v>
       </c>
       <c r="V50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X50" t="b">
         <v>0</v>
@@ -7104,10 +6955,10 @@
         <v>0</v>
       </c>
       <c r="Z50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="b">
         <v>0</v>
@@ -7122,10 +6973,10 @@
         <v>0</v>
       </c>
       <c r="AF50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="b">
         <v>0</v>
@@ -7140,15 +6991,12 @@
         <v>0</v>
       </c>
       <c r="AL50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7207,13 +7055,13 @@
         <v>0</v>
       </c>
       <c r="P51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="b">
         <v>1</v>
       </c>
       <c r="R51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="b">
         <v>0</v>
@@ -7222,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="U51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W51" t="b">
         <v>0</v>
@@ -7237,10 +7085,10 @@
         <v>0</v>
       </c>
       <c r="Z51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="b">
         <v>0</v>
@@ -7267,21 +7115,18 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK51" t="b">
         <v>1</v>
       </c>
       <c r="AL51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM51" t="b">
         <v>0</v>
       </c>
       <c r="AN51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7406,15 +7251,12 @@
         <v>0</v>
       </c>
       <c r="AL52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7473,7 +7315,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="b">
         <v>1</v>
@@ -7482,7 +7324,7 @@
         <v>1</v>
       </c>
       <c r="S53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" t="b">
         <v>0</v>
@@ -7545,9 +7387,6 @@
         <v>0</v>
       </c>
       <c r="AN53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO53" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7603,7 +7442,7 @@
         <v>1</v>
       </c>
       <c r="O54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" t="b">
         <v>1</v>
@@ -7618,19 +7457,19 @@
         <v>1</v>
       </c>
       <c r="T54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="b">
         <v>0</v>
@@ -7639,13 +7478,13 @@
         <v>0</v>
       </c>
       <c r="AA54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB54" t="b">
         <v>1</v>
       </c>
       <c r="AC54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="b">
         <v>0</v>
@@ -7666,7 +7505,7 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK54" t="b">
         <v>1</v>
@@ -7678,9 +7517,6 @@
         <v>1</v>
       </c>
       <c r="AN54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO54" t="b">
         <v>0</v>
       </c>
     </row>
@@ -7736,10 +7572,10 @@
         <v>1</v>
       </c>
       <c r="O55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="b">
         <v>0</v>
@@ -7754,13 +7590,13 @@
         <v>0</v>
       </c>
       <c r="U55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" t="b">
         <v>1</v>
       </c>
       <c r="W55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X55" t="b">
         <v>0</v>
@@ -7781,10 +7617,10 @@
         <v>0</v>
       </c>
       <c r="AD55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="b">
         <v>0</v>
@@ -7805,15 +7641,12 @@
         <v>0</v>
       </c>
       <c r="AL55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM55" t="b">
         <v>1</v>
       </c>
       <c r="AN55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO55" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7881,7 +7714,7 @@
         <v>1</v>
       </c>
       <c r="S56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" t="b">
         <v>0</v>
@@ -7893,10 +7726,10 @@
         <v>0</v>
       </c>
       <c r="W56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56" t="b">
         <v>0</v>
@@ -7917,13 +7750,13 @@
         <v>0</v>
       </c>
       <c r="AE56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF56" t="b">
         <v>1</v>
       </c>
       <c r="AG56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="b">
         <v>0</v>
@@ -7938,15 +7771,12 @@
         <v>0</v>
       </c>
       <c r="AL56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM56" t="b">
         <v>1</v>
       </c>
       <c r="AN56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8005,7 +7835,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="b">
         <v>1</v>
@@ -8014,13 +7844,13 @@
         <v>1</v>
       </c>
       <c r="S57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V57" t="b">
         <v>0</v>
@@ -8044,10 +7874,10 @@
         <v>0</v>
       </c>
       <c r="AC57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
@@ -8059,10 +7889,10 @@
         <v>0</v>
       </c>
       <c r="AH57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="b">
         <v>0</v>
@@ -8071,15 +7901,12 @@
         <v>0</v>
       </c>
       <c r="AL57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO57" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8135,7 +7962,7 @@
         <v>1</v>
       </c>
       <c r="O58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -8147,25 +7974,25 @@
         <v>1</v>
       </c>
       <c r="S58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" t="b">
         <v>0</v>
       </c>
       <c r="U58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" t="b">
         <v>1</v>
       </c>
       <c r="W58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="b">
         <v>0</v>
@@ -8189,10 +8016,10 @@
         <v>0</v>
       </c>
       <c r="AG58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="b">
         <v>0</v>
@@ -8204,15 +8031,12 @@
         <v>0</v>
       </c>
       <c r="AL58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM58" t="b">
         <v>1</v>
       </c>
       <c r="AN58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO58" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8268,7 +8092,7 @@
         <v>1</v>
       </c>
       <c r="O59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
@@ -8280,28 +8104,28 @@
         <v>1</v>
       </c>
       <c r="S59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" t="b">
         <v>0</v>
       </c>
       <c r="U59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X59" t="b">
         <v>1</v>
       </c>
       <c r="Y59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="b">
         <v>0</v>
@@ -8328,24 +8152,21 @@
         <v>0</v>
       </c>
       <c r="AI59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL59" t="b">
         <v>1</v>
       </c>
       <c r="AM59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO59" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8407,10 +8228,10 @@
         <v>0</v>
       </c>
       <c r="Q60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="b">
         <v>0</v>
@@ -8422,10 +8243,10 @@
         <v>0</v>
       </c>
       <c r="V60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X60" t="b">
         <v>0</v>
@@ -8434,10 +8255,10 @@
         <v>0</v>
       </c>
       <c r="Z60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="b">
         <v>0</v>
@@ -8452,10 +8273,10 @@
         <v>0</v>
       </c>
       <c r="AF60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="b">
         <v>0</v>
@@ -8470,15 +8291,12 @@
         <v>0</v>
       </c>
       <c r="AL60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO60" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8537,13 +8355,13 @@
         <v>0</v>
       </c>
       <c r="P61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="b">
         <v>1</v>
       </c>
       <c r="R61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="b">
         <v>0</v>
@@ -8552,10 +8370,10 @@
         <v>0</v>
       </c>
       <c r="U61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W61" t="b">
         <v>0</v>
@@ -8567,10 +8385,10 @@
         <v>0</v>
       </c>
       <c r="Z61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="b">
         <v>0</v>
@@ -8597,21 +8415,18 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK61" t="b">
         <v>1</v>
       </c>
       <c r="AL61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM61" t="b">
         <v>0</v>
       </c>
       <c r="AN61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO61" t="b">
         <v>0</v>
       </c>
     </row>

--- a/survey_encoded.xlsx
+++ b/survey_encoded.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
+          <t>שלב התיק</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -790,7 +790,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
+          <t>שלב התיק</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -920,7 +920,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
+          <t>שלב התיק</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
+          <t>שלב התיק</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
+          <t>שלב התיק</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
+          <t>שלב התיק</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
+          <t>שלב התיק</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
+          <t>שלב התיק</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
+          <t>שלב התיק</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>שלב התיק (חדש / פעיל / ותיק)(לפי סולם של גיל התיק במחלקה)</t>
+          <t>שלב התיק</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
+          <t>אינטנסיביות הטיפול</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
+          <t>אינטנסיביות הטיפול</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
+          <t>אינטנסיביות הטיפול</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
+          <t>אינטנסיביות הטיפול</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
+          <t>אינטנסיביות הטיפול</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
+          <t>אינטנסיביות הטיפול</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
+          <t>אינטנסיביות הטיפול</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
+          <t>אינטנסיביות הטיפול</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
+          <t>אינטנסיביות הטיפול</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>רמת אינטנסיביות הטיפול ( לפי מספר העדכונים בתיק בחודש)</t>
+          <t>אינטנסיביות הטיפול</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
+          <t>מספר בני המשפחה המעורבים</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
+          <t>מספר בני המשפחה המעורבים</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
+          <t>מספר בני המשפחה המעורבים</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
+          <t>מספר בני המשפחה המעורבים</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
+          <t>מספר בני המשפחה המעורבים</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
+          <t>מספר בני המשפחה המעורבים</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
+          <t>מספר בני המשפחה המעורבים</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
+          <t>מספר בני המשפחה המעורבים</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
+          <t>מספר בני המשפחה המעורבים</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>מספר בני המשפחה המעורבים (לפי מס׳ בני המשפחה שנכללים בתיק)</t>
+          <t>מספר בני המשפחה המעורבים</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
+          <t>ריבוי בעיות</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
+          <t>ריבוי בעיות</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
+          <t>ריבוי בעיות</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
+          <t>ריבוי בעיות</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
+          <t>ריבוי בעיות</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
+          <t>ריבוי בעיות</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
+          <t>ריבוי בעיות</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
+          <t>ריבוי בעיות</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
+          <t>ריבוי בעיות</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ריבוי בעיות ותחומי קושי(לפי מספר המאפיינים בתיק)</t>
+          <t>ריבוי בעיות</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
+          <t>מעורבות חוק</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
+          <t>מעורבות חוק</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
+          <t>מעורבות חוק</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
+          <t>מעורבות חוק</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
+          <t>מעורבות חוק</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
+          <t>מעורבות חוק</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
+          <t>מעורבות חוק</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
+          <t>מעורבות חוק</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
+          <t>מעורבות חוק</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>עבודה חוקית / רגולטורית ( האם יש מעורבות עו״ס לחוק)</t>
+          <t>מעורבות חוק</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
+          <t>עבודה בין מערכתית</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
+          <t>עבודה בין מערכתית</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
+          <t>עבודה בין מערכתית</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
+          <t>עבודה בין מערכתית</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
+          <t>עבודה בין מערכתית</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
+          <t>עבודה בין מערכתית</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
+          <t>עבודה בין מערכתית</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
+          <t>עבודה בין מערכתית</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
+          <t>עבודה בין מערכתית</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>עבודה בין מערכתית ( האם נדרשה וותת״ט ולפי מס גורמים נוספים שיש בתיק)</t>
+          <t>עבודה בין מערכתית</t>
         </is>
       </c>
       <c r="I61" t="n">
